--- a/port_data/estimation_universe_20260130.xlsx
+++ b/port_data/estimation_universe_20260130.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://5dimensionsenergycom-my.sharepoint.com/personal/francis_wu_5dimensionsenergy_com/Documents/Short term risk model/port_data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\OTC-User1\OTCProjects\Francis\repos\Short-term-risk-model\port_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_ECE9E8BB28141B4CB615BDF684093A99F7D8271A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2BB4516D-ABEB-4871-88D8-B2AB4BAA271F}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D00C711-4E8F-4608-8EA4-03CB02977431}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38510" yWindow="-9650" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11910" yWindow="3630" windowWidth="17280" windowHeight="15950" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Worksheet" sheetId="2" r:id="rId1"/>
@@ -18100,7 +18100,7 @@
     <t>TLN</t>
   </si>
   <si>
-    <t>Port</t>
+    <t>All</t>
   </si>
 </sst>
 </file>
@@ -18601,9 +18601,9 @@
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="33" borderId="0" xfId="26"/>
     <xf numFmtId="0" fontId="1" fillId="33" borderId="0" xfId="26"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="20% - Accent1" xfId="1" builtinId="30" customBuiltin="1"/>
@@ -18957,34 +18957,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
     </row>
@@ -19021,20 +19021,20 @@
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A4" s="3"/>
+      <c r="A4" s="1"/>
       <c r="B4" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="1"/>
+      <c r="C4" s="3"/>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="1" t="s">
         <v>6026</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="1" t="s">
         <v>21</v>
       </c>
     </row>
